--- a/AAII_Financials/Quarterly/DTM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DTM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>DTM</t>
   </si>
@@ -656,262 +656,269 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E8" s="3">
         <v>336000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>317000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>314000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>309000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>303000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>249000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>248000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>244000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>240000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>244000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>234000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>224000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>220000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>243000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>235000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>227000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>215000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>223000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>212000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>208000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>197000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>208000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>203000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>174000</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E9" s="3">
         <v>85000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>64000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>84000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>80000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>78000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>51000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>63000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>52000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>54000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>46000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>58000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>60000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>58000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -951,53 +958,56 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E10" s="3">
         <v>251000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>253000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>230000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>229000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>225000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>198000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>185000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>192000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>186000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>198000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>176000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>164000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>162000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1047,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,8 +1082,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1155,8 +1169,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,17 +1258,20 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,32 +1281,32 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>4000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-3000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1327,28 +1347,31 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E15" s="3">
         <v>69000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>67000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>65000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>63000</v>
       </c>
       <c r="H15" s="3">
         <v>63000</v>
       </c>
       <c r="I15" s="3">
-        <v>53000</v>
+        <v>63000</v>
       </c>
       <c r="J15" s="3">
         <v>53000</v>
@@ -1357,25 +1380,25 @@
         <v>53000</v>
       </c>
       <c r="L15" s="3">
+        <v>53000</v>
+      </c>
+      <c r="M15" s="3">
         <v>50000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>49000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>46000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>44000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>43000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>44000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>42000</v>
       </c>
       <c r="S15" s="3">
         <v>42000</v>
@@ -1390,7 +1413,7 @@
         <v>42000</v>
       </c>
       <c r="W15" s="3">
-        <v>41000</v>
+        <v>42000</v>
       </c>
       <c r="X15" s="3">
         <v>41000</v>
@@ -1399,22 +1422,25 @@
         <v>41000</v>
       </c>
       <c r="Z15" s="3">
+        <v>41000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>38000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>37000</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,180 +1468,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>170000</v>
+      </c>
+      <c r="E17" s="3">
         <v>169000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>161000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>159000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>154000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>155000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>136000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>126000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>114000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>116000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>124000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>111000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>110000</v>
       </c>
       <c r="P17" s="3">
         <v>110000</v>
       </c>
       <c r="Q17" s="3">
+        <v>110000</v>
+      </c>
+      <c r="R17" s="3">
         <v>127000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>114000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>90000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>111000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>113000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>106000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>122000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>97000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>114000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>79000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>74000</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E18" s="3">
         <v>167000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>156000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>155000</v>
       </c>
       <c r="G18" s="3">
         <v>155000</v>
       </c>
       <c r="H18" s="3">
+        <v>155000</v>
+      </c>
+      <c r="I18" s="3">
         <v>148000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>113000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>122000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>130000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>124000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>120000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>123000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>114000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>110000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>116000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>121000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>137000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>104000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>110000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>106000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>86000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>100000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>94000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>124000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>100000</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,191 +1679,198 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-43000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-39000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-37000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-30000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-37000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-41000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-36000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-42000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-46000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-45000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-41000</v>
       </c>
       <c r="O20" s="3">
         <v>-41000</v>
       </c>
       <c r="P20" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-51000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>45000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>37000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>23000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>36000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>35000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>31000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>30000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>36000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>34000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>49000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>25000</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E21" s="3">
         <v>279000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>262000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>257000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>248000</v>
       </c>
       <c r="H21" s="3">
         <v>248000</v>
       </c>
       <c r="I21" s="3">
+        <v>248000</v>
+      </c>
+      <c r="J21" s="3">
         <v>207000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>211000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>225000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>220000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>214000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>210000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>199000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>204000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>205000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>200000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>202000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>182000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>187000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>179000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>157000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>177000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>169000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>211000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>162000</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E22" s="3">
         <v>40000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>41000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>40000</v>
       </c>
       <c r="G22" s="3">
         <v>40000</v>
@@ -1839,40 +1879,40 @@
         <v>40000</v>
       </c>
       <c r="I22" s="3">
+        <v>40000</v>
+      </c>
+      <c r="J22" s="3">
         <v>36000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>38000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>40000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>39000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>38000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>35000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>38000</v>
       </c>
       <c r="Q22" s="3">
         <v>38000</v>
       </c>
       <c r="R22" s="3">
+        <v>38000</v>
+      </c>
+      <c r="S22" s="3">
         <v>35000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>33000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>31000</v>
       </c>
       <c r="U22" s="3">
         <v>31000</v>
@@ -1881,72 +1921,75 @@
         <v>31000</v>
       </c>
       <c r="W22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="X22" s="3">
         <v>24000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>26000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>31000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>29000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>26000</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E23" s="3">
         <v>170000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>154000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>153000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>145000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>146000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>119000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>121000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>133000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>131000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>126000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>127000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>124000</v>
-      </c>
-      <c r="P23" s="3">
-        <v>123000</v>
       </c>
       <c r="Q23" s="3">
         <v>123000</v>
@@ -1955,129 +1998,135 @@
         <v>123000</v>
       </c>
       <c r="S23" s="3">
+        <v>123000</v>
+      </c>
+      <c r="T23" s="3">
         <v>127000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>109000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>114000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>106000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>92000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>110000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>97000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>144000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>99000</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E24" s="3">
         <v>36000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>40000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>35000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>34000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>35000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>43000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>30000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>33000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>31000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>33000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>30000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>39000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>35000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>33000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>25000</v>
       </c>
       <c r="U24" s="3">
         <v>25000</v>
       </c>
       <c r="V24" s="3">
+        <v>25000</v>
+      </c>
+      <c r="W24" s="3">
         <v>29000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>29000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>25000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>39000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>26000</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,180 +2211,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E26" s="3">
         <v>134000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>114000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>118000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>111000</v>
       </c>
       <c r="H26" s="3">
         <v>111000</v>
       </c>
       <c r="I26" s="3">
+        <v>111000</v>
+      </c>
+      <c r="J26" s="3">
         <v>76000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>91000</v>
-      </c>
-      <c r="K26" s="3">
-        <v>100000</v>
       </c>
       <c r="L26" s="3">
         <v>100000</v>
       </c>
       <c r="M26" s="3">
+        <v>100000</v>
+      </c>
+      <c r="N26" s="3">
         <v>124000</v>
-      </c>
-      <c r="N26" s="3">
-        <v>94000</v>
       </c>
       <c r="O26" s="3">
         <v>94000</v>
       </c>
       <c r="P26" s="3">
+        <v>94000</v>
+      </c>
+      <c r="Q26" s="3">
         <v>84000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>88000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>116000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>94000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>84000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>89000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>77000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>71000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>81000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>72000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>105000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>73000</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E27" s="3">
         <v>130000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>111000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>115000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>107000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>108000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>73000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>88000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>96000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>97000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>121000</v>
-      </c>
-      <c r="N27" s="3">
-        <v>91000</v>
       </c>
       <c r="O27" s="3">
         <v>91000</v>
       </c>
       <c r="P27" s="3">
+        <v>91000</v>
+      </c>
+      <c r="Q27" s="3">
         <v>81000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>85000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>113000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>91000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>81000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>87000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>74000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>68000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>78000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>69000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>101000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>71000</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2478,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2506,8 +2567,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2656,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,180 +2745,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E32" s="3">
         <v>43000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>39000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>37000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>30000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>37000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>41000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>36000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>42000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>46000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>45000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>41000</v>
       </c>
       <c r="O32" s="3">
         <v>41000</v>
       </c>
       <c r="P32" s="3">
+        <v>41000</v>
+      </c>
+      <c r="Q32" s="3">
         <v>51000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-45000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-37000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-23000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-36000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-35000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-31000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-30000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-34000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E33" s="3">
         <v>130000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>111000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>115000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>107000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>108000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>73000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>88000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>96000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>97000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>121000</v>
-      </c>
-      <c r="N33" s="3">
-        <v>91000</v>
       </c>
       <c r="O33" s="3">
         <v>91000</v>
       </c>
       <c r="P33" s="3">
+        <v>91000</v>
+      </c>
+      <c r="Q33" s="3">
         <v>81000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>85000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>113000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>91000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>81000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>87000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>74000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>68000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>78000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>69000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>101000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>71000</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,185 +3012,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E35" s="3">
         <v>130000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>111000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>115000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>107000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>108000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>73000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>88000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>96000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>97000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>121000</v>
-      </c>
-      <c r="N35" s="3">
-        <v>91000</v>
       </c>
       <c r="O35" s="3">
         <v>91000</v>
       </c>
       <c r="P35" s="3">
+        <v>91000</v>
+      </c>
+      <c r="Q35" s="3">
         <v>81000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>85000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>113000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>91000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>81000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>87000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>74000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>68000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>78000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>69000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>101000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>71000</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3230,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,77 +3263,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E41" s="3">
         <v>150000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>54000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>98000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>74000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>83000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>68000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>77000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>73000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>56000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>45000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>95000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>61000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>355000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>345000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>281000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>132000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>128000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>37000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>29000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3263,8 +3350,11 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3349,77 +3439,80 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E43" s="3">
         <v>190000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>188000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>175000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>164000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>168000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>180000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>143000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>155000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>150000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>169000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>146000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>144000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>122000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>161000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>150000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>137000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>124000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>178000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>155000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>118000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>380000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3435,8 +3528,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3479,8 +3575,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3521,77 +3617,80 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E45" s="3">
         <v>32000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>42000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>40000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>28000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>33000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>37000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>50000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>27000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>25000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>32000</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,77 +3706,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E46" s="3">
         <v>404000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>318000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>322000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>291000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>312000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>310000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>249000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>256000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>229000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>272000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>200000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>210000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>249000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>262000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>533000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>515000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>442000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>360000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>310000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>180000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>441000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3693,77 +3795,80 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1243000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1245000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1253000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1262000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1288000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1286000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1297000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1301000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1725000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1735000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1762000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1782000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1789000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2171000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2204000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1678000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1681000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1684000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1693000</v>
-      </c>
-      <c r="V47" s="3">
-        <v>1691000</v>
       </c>
       <c r="W47" s="3">
         <v>1691000</v>
       </c>
       <c r="X47" s="3">
+        <v>1691000</v>
+      </c>
+      <c r="Y47" s="3">
         <v>1701000</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3779,77 +3884,80 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5895000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5830000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5812000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5766000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5655000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5596000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5576000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4596000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4559000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4525000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4472000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4390000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4224000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4042000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3837000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3666000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3537000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3514000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3526000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3524000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3506000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3502000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,77 +3973,80 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2613000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2628000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2643000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2658000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2673000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2683000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2697000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2398000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2412000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2426000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2441000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2455000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2469000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2484000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2498000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2512000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2527000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2541000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2555000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2570000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2584000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2598000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3951,8 +4062,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4151,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,55 +4240,58 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E52" s="3">
         <v>43000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>44000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>43000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>34000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>44000</v>
       </c>
       <c r="I52" s="3">
         <v>44000</v>
       </c>
       <c r="J52" s="3">
+        <v>44000</v>
+      </c>
+      <c r="K52" s="3">
         <v>34000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>31000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>32000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>30000</v>
       </c>
       <c r="S52" s="3">
         <v>30000</v>
@@ -4180,20 +4300,20 @@
         <v>30000</v>
       </c>
       <c r="U52" s="3">
-        <v>32000</v>
+        <v>30000</v>
       </c>
       <c r="V52" s="3">
         <v>32000</v>
       </c>
       <c r="W52" s="3">
+        <v>32000</v>
+      </c>
+      <c r="X52" s="3">
         <v>29000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>22000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,8 +4329,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,77 +4418,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10207000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10155000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10080000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10061000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9960000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9932000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9935000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8587000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8986000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8951000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8982000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8862000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8726000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8981000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8833000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8419000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8290000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8211000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8166000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8127000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7990000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8264000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4381,8 +4507,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4542,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,77 +4575,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E57" s="3">
         <v>57000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>65000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>96000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>84000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>67000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>77000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>67000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>68000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>94000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>124000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>125000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>107000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>119000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>71000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>32000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>21000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>22000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>30000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>26000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>28000</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,61 +4662,64 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E58" s="3">
         <v>17000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>41000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>79000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>166000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>87000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>70000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>178000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>140000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>116000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>427000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>330000</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>10000</v>
@@ -4597,11 +4731,11 @@
         <v>10000</v>
       </c>
       <c r="X58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="Y58" s="3">
         <v>3021000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4617,8 +4751,11 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4626,68 +4763,68 @@
         <v>140000</v>
       </c>
       <c r="E59" s="3">
+        <v>140000</v>
+      </c>
+      <c r="F59" s="3">
         <v>131000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>138000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>145000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>138000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>110000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>103000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>107000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>108000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>91000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>78000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>97000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>165000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>178000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>148000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>157000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>145000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>155000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>71000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>63000</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,77 +4840,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>298000</v>
+      </c>
+      <c r="E60" s="3">
         <v>321000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>296000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>349000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>331000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>381000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>426000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>262000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>306000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>322000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>434000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>424000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>361000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>698000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>614000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>249000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>180000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>188000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>177000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>195000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>107000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3112000</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +4929,11 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4798,64 +4941,64 @@
         <v>3354000</v>
       </c>
       <c r="E61" s="3">
+        <v>3354000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3356000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>3358000</v>
       </c>
       <c r="G61" s="3">
         <v>3358000</v>
       </c>
       <c r="H61" s="3">
+        <v>3358000</v>
+      </c>
+      <c r="I61" s="3">
         <v>3354000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3355000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2708000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>3105000</v>
       </c>
       <c r="L61" s="3">
         <v>3105000</v>
       </c>
       <c r="M61" s="3">
+        <v>3105000</v>
+      </c>
+      <c r="N61" s="3">
         <v>3092000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3094000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3092000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3089000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3059000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3058000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3057000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3033000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3036000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>3037000</v>
       </c>
       <c r="W61" s="3">
         <v>3037000</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>3037000</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -4875,77 +5018,80 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>120000</v>
+        <v>122000</v>
       </c>
       <c r="E62" s="3">
         <v>120000</v>
       </c>
       <c r="F62" s="3">
+        <v>120000</v>
+      </c>
+      <c r="G62" s="3">
         <v>119000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>117000</v>
       </c>
       <c r="H62" s="3">
         <v>117000</v>
       </c>
       <c r="I62" s="3">
+        <v>117000</v>
+      </c>
+      <c r="J62" s="3">
         <v>124000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>25000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>33000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>34000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>109000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>93000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>70000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1006000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>987000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>982000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>952000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>932000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>906000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>865000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>848000</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4961,8 +5107,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5196,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5285,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,77 +5374,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5286000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5260000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5202000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5217000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5145000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5150000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5169000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4231000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4649000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4645000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4702000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4641000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4531000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4816000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4826000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4441000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4367000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4321000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4294000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4288000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4160000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4111000</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5305,8 +5463,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5498,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5585,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5674,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5595,8 +5763,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,77 +5852,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>888000</v>
+      </c>
+      <c r="E72" s="3">
         <v>867000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>827000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>801000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>770000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>747000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>723000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>726000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>710000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>686000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>661000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>608000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>584000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>561000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>547000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>523000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>473000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>446000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>431000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>403000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>386000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>831000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5767,8 +5941,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6030,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6119,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,77 +6208,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4779000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4753000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4736000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4702000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4673000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4642000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4627000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4218000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4197000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4166000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4139000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4079000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4052000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4023000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4007000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3978000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3923000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3890000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3872000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3839000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3830000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4153000</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6297,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,185 +6386,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E81" s="3">
         <v>130000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>111000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>115000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>107000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>108000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>73000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>88000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>96000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>97000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>121000</v>
-      </c>
-      <c r="N81" s="3">
-        <v>91000</v>
       </c>
       <c r="O81" s="3">
         <v>91000</v>
       </c>
       <c r="P81" s="3">
+        <v>91000</v>
+      </c>
+      <c r="Q81" s="3">
         <v>81000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>85000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>113000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>91000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>81000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>87000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>74000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>68000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>78000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>69000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>101000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>71000</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,55 +6604,56 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E83" s="3">
         <v>67000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>57000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>58000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>54000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>53000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>51000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>48000</v>
       </c>
       <c r="L83" s="3">
         <v>48000</v>
       </c>
       <c r="M83" s="3">
+        <v>48000</v>
+      </c>
+      <c r="N83" s="3">
         <v>49000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>47000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>46000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>47000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>44000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>42000</v>
       </c>
       <c r="S83" s="3">
         <v>42000</v>
@@ -6469,7 +6668,7 @@
         <v>42000</v>
       </c>
       <c r="W83" s="3">
-        <v>41000</v>
+        <v>42000</v>
       </c>
       <c r="X83" s="3">
         <v>41000</v>
@@ -6478,22 +6677,25 @@
         <v>41000</v>
       </c>
       <c r="Z83" s="3">
+        <v>41000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>38000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>37000</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6780,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6869,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6958,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7047,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,94 +7136,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>222000</v>
+      </c>
+      <c r="E89" s="3">
         <v>280000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>161000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>274000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>185000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>247000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>152000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>205000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>165000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>241000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>184000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>225000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>145000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>244000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>151000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>195000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>145000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>234000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>108000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>136000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>165000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>163000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>143000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>157000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>164000</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,94 +7260,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-78000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-131000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-143000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-81000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-71000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-90000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-81000</v>
       </c>
       <c r="K91" s="3">
         <v>-81000</v>
       </c>
       <c r="L91" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-98000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-150000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-201000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-193000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-228000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-165000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-118000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-35000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-44000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-33000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-78000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-94000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-210000</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7436,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,94 +7525,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-68000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-118000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-130000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-70000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-54000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1284000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>346000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-72000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-71000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-128000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-192000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>185000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-216000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-704000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-119000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-14000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-17000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-40000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-38000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>218000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-17000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-113000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-102000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-347000</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,13 +7649,14 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>83000</v>
+        <v>89000</v>
       </c>
       <c r="E96" s="3">
         <v>83000</v>
@@ -7434,10 +7668,10 @@
         <v>83000</v>
       </c>
       <c r="H96" s="3">
+        <v>83000</v>
+      </c>
+      <c r="I96" s="3">
         <v>75000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>71000</v>
       </c>
       <c r="J96" s="3">
         <v>71000</v>
@@ -7446,7 +7680,7 @@
         <v>71000</v>
       </c>
       <c r="L96" s="3">
-        <v>67000</v>
+        <v>71000</v>
       </c>
       <c r="M96" s="3">
         <v>67000</v>
@@ -7458,26 +7692,26 @@
         <v>67000</v>
       </c>
       <c r="P96" s="3">
+        <v>67000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>62000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>58000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-58000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>443000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -7502,8 +7736,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7825,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7914,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,94 +8003,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-116000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-87000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-120000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-124000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-178000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1123000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-547000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-61000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-185000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-30000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-48000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-380000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>259000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-66000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-67000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-68000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-64000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-375000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-159000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-43000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>68000</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7890,8 +8139,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7932,90 +8181,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E102" s="3">
         <v>96000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-44000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>24000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>32000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-50000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>34000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-294000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>10000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>64000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>149000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>91000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8000</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-13000</v>
       </c>
       <c r="Y102" s="3">
         <v>-13000</v>
       </c>
       <c r="Z102" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-115000</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
